--- a/artfynd/A 41360-2025 artfynd.xlsx
+++ b/artfynd/A 41360-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105940635</v>
+        <v>192186</v>
       </c>
       <c r="B2" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2082</v>
+        <v>165</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Topplåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Botrychium lanceolatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(S. G. Gmel.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lomtjärnbergets nordsluttning, 14km NNO om Tåsjö kyrka, Ås lm</t>
+          <t>Bellvik 8km NV,Dorotea,, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548863</v>
+        <v>549204</v>
       </c>
       <c r="R2" t="n">
-        <v>7135226</v>
+        <v>7135531</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2011-07-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2011-07-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,69 +770,83 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Göran Frisk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Göran Frisk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105940640</v>
+        <v>237510</v>
       </c>
       <c r="B3" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2082</v>
+        <v>167</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(S. G. Gmel.) Rupr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lomtjärnbergets nordsluttning, 14km NNO om Tåsjö kyrka, Ås lm</t>
+          <t>Bellvik 8km NV,Dorotea,, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548684</v>
+        <v>549204</v>
       </c>
       <c r="R3" t="n">
-        <v>7135241</v>
+        <v>7135531</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +870,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2011-07-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2011-07-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mest bara blad</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +895,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Göran Frisk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Göran Frisk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105940637</v>
+        <v>105940630</v>
       </c>
       <c r="B4" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,14 +938,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomtjärnbergets nordsluttning, 14km NNO om Tåsjö kyrka, Ås lm</t>
+          <t>Lomtjärnbergets ostsluttning, 15km NNO om Tåsjö kyrka, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548774</v>
+        <v>549104</v>
       </c>
       <c r="R4" t="n">
-        <v>7135234</v>
+        <v>7135346</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105940642</v>
+        <v>105940631</v>
       </c>
       <c r="B5" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,14 +1035,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lomtjärnbergets nordsluttning, 14km NNO om Tåsjö kyrka, Ås lm</t>
+          <t>Lomtjärnbergets ostsluttning, 15km NNO om Tåsjö kyrka, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548629</v>
+        <v>549087</v>
       </c>
       <c r="R5" t="n">
-        <v>7135246</v>
+        <v>7135310</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105940630</v>
+        <v>105940632</v>
       </c>
       <c r="B6" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,14 +1132,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomtjärnbergets ostsluttning, 15km NNO om Tåsjö kyrka, Ås lm</t>
+          <t>Lomtjärnbergets nordsluttning, 14km NNO om Tåsjö kyrka, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549104</v>
+        <v>548924</v>
       </c>
       <c r="R6" t="n">
-        <v>7135346</v>
+        <v>7135221</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105940646</v>
+        <v>105940633</v>
       </c>
       <c r="B7" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>2082</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548453.0404538902</v>
+        <v>548906</v>
       </c>
       <c r="R7" t="n">
-        <v>7135259.08200822</v>
+        <v>7135222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,19 +1266,9 @@
           <t>2022-09-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,15 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105940667</v>
+        <v>105940635</v>
       </c>
       <c r="B8" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548290</v>
+        <v>548863</v>
       </c>
       <c r="R8" t="n">
-        <v>7135248</v>
+        <v>7135226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,15 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105940647</v>
+        <v>105940636</v>
       </c>
       <c r="B9" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548453</v>
+        <v>548798</v>
       </c>
       <c r="R9" t="n">
-        <v>7135259</v>
+        <v>7135232</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,15 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105940649</v>
+        <v>105940637</v>
       </c>
       <c r="B10" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548410</v>
+        <v>548774</v>
       </c>
       <c r="R10" t="n">
-        <v>7135259</v>
+        <v>7135234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,12 +1589,7 @@
         <v>105940638</v>
       </c>
       <c r="B11" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,15 +1683,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105940636</v>
+        <v>105940639</v>
       </c>
       <c r="B12" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,10 +1718,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548798</v>
+        <v>548714</v>
       </c>
       <c r="R12" t="n">
-        <v>7135232</v>
+        <v>7135239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,15 +1780,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105940631</v>
+        <v>105940640</v>
       </c>
       <c r="B13" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,14 +1811,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lomtjärnbergets ostsluttning, 15km NNO om Tåsjö kyrka, Ås lm</t>
+          <t>Lomtjärnbergets nordsluttning, 14km NNO om Tåsjö kyrka, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549087</v>
+        <v>548684</v>
       </c>
       <c r="R13" t="n">
-        <v>7135310</v>
+        <v>7135241</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,15 +1877,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105940645</v>
+        <v>105940641</v>
       </c>
       <c r="B14" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548500</v>
+        <v>548654</v>
       </c>
       <c r="R14" t="n">
-        <v>7135257</v>
+        <v>7135244</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,15 +1974,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105940633</v>
+        <v>105940642</v>
       </c>
       <c r="B15" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548906</v>
+        <v>548629</v>
       </c>
       <c r="R15" t="n">
-        <v>7135222</v>
+        <v>7135246</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,12 +2074,7 @@
         <v>105940643</v>
       </c>
       <c r="B16" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2215,15 +2168,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105940632</v>
+        <v>105940644</v>
       </c>
       <c r="B17" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548924</v>
+        <v>548555</v>
       </c>
       <c r="R17" t="n">
-        <v>7135221</v>
+        <v>7135252</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,15 +2265,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105940641</v>
+        <v>105940645</v>
       </c>
       <c r="B18" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548654</v>
+        <v>548500</v>
       </c>
       <c r="R18" t="n">
-        <v>7135244</v>
+        <v>7135257</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,15 +2362,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105940639</v>
+        <v>105940647</v>
       </c>
       <c r="B19" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2459,10 +2397,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548714</v>
+        <v>548453</v>
       </c>
       <c r="R19" t="n">
-        <v>7135239</v>
+        <v>7135259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,15 +2459,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105940644</v>
+        <v>105940648</v>
       </c>
       <c r="B20" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,10 +2494,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548555</v>
+        <v>548427</v>
       </c>
       <c r="R20" t="n">
-        <v>7135252</v>
+        <v>7135260</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,15 +2556,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105940629</v>
+        <v>105940649</v>
       </c>
       <c r="B21" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,34 +2567,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219880</v>
+        <v>2082</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lomtjärnbergets ostsluttning, 15km NNO om Tåsjö kyrka, Ås lm</t>
+          <t>Lomtjärnbergets nordsluttning, 14km NNO om Tåsjö kyrka, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549103.6819094005</v>
+        <v>548410</v>
       </c>
       <c r="R21" t="n">
-        <v>7135346.156605859</v>
+        <v>7135259</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,19 +2624,9 @@
           <t>2022-09-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,15 +2653,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105940648</v>
+        <v>105940667</v>
       </c>
       <c r="B22" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,10 +2688,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548427</v>
+        <v>548290</v>
       </c>
       <c r="R22" t="n">
-        <v>7135260</v>
+        <v>7135248</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2834,6 +2747,311 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>105940629</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lomtjärnbergets ostsluttning, 15km NNO om Tåsjö kyrka, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>549104</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7135346</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>105940646</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lomtjärnbergets nordsluttning, 14km NNO om Tåsjö kyrka, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>548453</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7135259</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4542742</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bellvik 8km NV,Dorotea,, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>549204</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7135531</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2011-07-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2011-07-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
